--- a/dist/anime_palettes.xlsx
+++ b/dist/anime_palettes.xlsx
@@ -22462,7 +22462,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -41733,7 +41733,7 @@
       </c>
       <c r="F164" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G164" s="505" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="F165" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G165" s="505" t="inlineStr">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="F166" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G166" s="505" t="inlineStr">
@@ -42072,7 +42072,7 @@
       </c>
       <c r="F167" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G167" s="505" t="inlineStr">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="F168" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G168" s="505" t="inlineStr">
@@ -42298,7 +42298,7 @@
       </c>
       <c r="F169" s="505" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>粉</t>
         </is>
       </c>
       <c r="G169" s="505" t="inlineStr">
